--- a/nr-add-mapping/ig/ValueSet-as-vs-source-information-installation.xlsx
+++ b/nr-add-mapping/ig/ValueSet-as-vs-source-information-installation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
